--- a/artfynd/A 31661-2024 artfynd.xlsx
+++ b/artfynd/A 31661-2024 artfynd.xlsx
@@ -2809,6 +2809,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vigdsjön, Ång</t>
@@ -2855,7 +2860,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Kläckhål och gnaggångar på björkhögstubbe med levande fnösktickor</t>
+          <t>Osäker artbestämning. Kläckhål och gnaggångar på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,6 +2869,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31661-2024 artfynd.xlsx
+++ b/artfynd/A 31661-2024 artfynd.xlsx
@@ -3304,11 +3304,11 @@
         <v>120639051</v>
       </c>
       <c r="B27" t="n">
-        <v>91119</v>
+        <v>91168</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/artfynd/A 31661-2024 artfynd.xlsx
+++ b/artfynd/A 31661-2024 artfynd.xlsx
@@ -3304,7 +3304,7 @@
         <v>120639051</v>
       </c>
       <c r="B27" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 31661-2024 artfynd.xlsx
+++ b/artfynd/A 31661-2024 artfynd.xlsx
@@ -3304,7 +3304,7 @@
         <v>120639051</v>
       </c>
       <c r="B27" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 31661-2024 artfynd.xlsx
+++ b/artfynd/A 31661-2024 artfynd.xlsx
@@ -3304,7 +3304,7 @@
         <v>120639051</v>
       </c>
       <c r="B27" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 31661-2024 artfynd.xlsx
+++ b/artfynd/A 31661-2024 artfynd.xlsx
@@ -3304,7 +3304,7 @@
         <v>120639051</v>
       </c>
       <c r="B27" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
